--- a/Lista_de_materiais_04.01.3.000598_estilo_Nomus.xlsx
+++ b/Lista_de_materiais_04.01.3.000598_estilo_Nomus.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1069,9 +1069,9 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                03.022-007314 - CHAPA 1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1084,94 +1084,94 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>03.022-007313</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.022-007314</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                03.022-007314 - CHAPA 1</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                    01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>6.14</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>03.022-007314</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>01.09.3.1.1.5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                03.022-007315 - CHAPA 2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>03.022-007306</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>03.022-007314</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>03.022-007314</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.3</t>
+          <t>03.022-007315</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">                    01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>11.76</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>03.022-007314</t>
+          <t>03.022-007315</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                03.022-007315 - CHAPA 2</t>
+          <t xml:space="preserve">                03.022-007316 - NERVURA 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>03.022-007315</t>
+          <t>03.022-007316</t>
         </is>
       </c>
     </row>
@@ -1205,11 +1205,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11.76</v>
+        <v>2.36</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>03.022-007315</t>
+          <t>03.022-007316</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1219,9 +1219,9 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                03.022-007317 - NERVURA 2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1230,248 +1230,248 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>03.022-007315</t>
+          <t>03.022-007306</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.022-007317</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                03.022-007316 - NERVURA 1</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                    01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>6.16</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>03.022-007306</t>
+          <t>03.022-007317</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>03.022-007316</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007355 - SUPORTE DO DISTRIBUIDOR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.36</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>03.022-007316</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.3</t>
+          <t>03.022-007355</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.09.3.1.1.5.19 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>0.86</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>03.022-007316</t>
+          <t>03.022-007355</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>01.09.3.1.1.5.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>03.022-007355</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>09.1.0003</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                03.022-007317 - NERVURA 2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>03.022-007306</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>03.022-007317</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007326 - ANEL GUARDA PÓ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6.16</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>03.022-007317</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.3</t>
+          <t>03.022-007326</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>03.022-007317</t>
+          <t>03.022-007326</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>01.09.3.1.2.4.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>03.022-007326</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>09.1.0003</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007355 - SUPORTE DO DISTRIBUIDOR</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>03.022-007355</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.3.1.1.5.19 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/8"</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007328 - ANEL LANTERNA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.86</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>03.022-007355</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.19</t>
+          <t>03.022-007328</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.09.1.1.30.3.1 - BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>03.022-007355</t>
+          <t>03.022-007328</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.1.1.30.3.1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007326 - ANEL GUARDA PÓ</t>
+          <t xml:space="preserve">    03.022-007327 - ANEL ANTI EXTRUSÃO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1489,39 +1489,39 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>03.022-007326</t>
+          <t>03.022-007327</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+          <t xml:space="preserve">        01.09.1.1.30.3.1 - BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.18</v>
+        <v>30</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>03.022-007326</t>
+          <t>03.022-007327</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.11</t>
+          <t>01.09.1.1.30.3.1</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007368 - CONJUNTO JANELA DE VISITA USINADA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1534,19 +1534,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>03.022-007326</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.022-007368</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007328 - ANEL LANTERNA</t>
+          <t xml:space="preserve">        03.022-007369 - CONJUNTO JANELA DE VISITA SOLDADA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1559,94 +1559,94 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007368</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>03.022-007328</t>
+          <t>03.022-007369</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.1.1.30.3.1 - BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007365 - FLANGE DA TAMPA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>03.022-007328</t>
+          <t>03.022-007369</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01.09.1.1.30.3.1</t>
+          <t>03.022-007365</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007327 - ANEL ANTI EXTRUSÃO</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.09.3.1.2.4.6 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>30.16</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007365</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>03.022-007327</t>
+          <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.1.1.30.3.1 - BARRA REDONDA 3 1/2" AÇO INOX AISI 304</t>
+          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>03.022-007327</t>
+          <t>03.022-007365</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>01.09.1.1.30.3.1</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007368 - CONJUNTO JANELA DE VISITA USINADA</t>
+          <t xml:space="preserve">            03.022-007367 - TUBO DA TAMPA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1659,44 +1659,44 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007369</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>03.022-007368</t>
+          <t>03.022-007367</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        03.022-007369 - CONJUNTO JANELA DE VISITA SOLDADA</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.13.1.5.4.4 - TUBO 1" ASTM A36 SCH 80</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>03.022-007368</t>
+          <t>03.022-007367</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>03.022-007369</t>
+          <t>01.13.1.5.4.4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007365 - FLANGE DA TAMPA</t>
+          <t xml:space="preserve">            03.022-007366 - NERVURA DA TAMPA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>03.022-007365</t>
+          <t>03.022-007366</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.09.3.1.2.4.6 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+          <t xml:space="preserve">                01.09.3.1.1.5.11 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1730,23 +1730,23 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30.16</v>
+        <v>2.36</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>03.022-007365</t>
+          <t>03.022-007366</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.6</t>
+          <t>01.09.3.1.1.5.11</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007329 - PREME GAXETA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1759,144 +1759,144 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>03.022-007365</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.022-007329</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007367 - TUBO DA TAMPA</t>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        01.09.3.1.1.5.4 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>03.022-007369</t>
+          <t>03.022-007329</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>03.022-007367</t>
+          <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                01.13.1.5.4.4 - TUBO 1" ASTM A36 SCH 80</t>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007330 - PRENSA GAXETA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03.022-007367</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>01.13.1.5.4.4</t>
+          <t>03.022-007330</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007366 - NERVURA DA TAMPA</t>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>03.022-007369</t>
+          <t>03.022-007330</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>03.022-007366</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                01.09.3.1.1.5.11 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 1/2"</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007334 - CHAVETA CENTRAL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.36</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>03.022-007366</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.11</t>
+          <t>03.022-007334</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.09.1.10.224.1.22 - BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>03.022-007366</t>
+          <t>03.022-007334</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.1.10.224.1.22</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007329 - PREME GAXETA</t>
+          <t xml:space="preserve">    03.022-007318 - EIXO PRINCIPAL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1914,64 +1914,64 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>03.022-007329</t>
+          <t>03.022-007318</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.3.1.1.5.4 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+          <t xml:space="preserve">        01.09.1.1.27.3.7 - BARRA REDONDA 3" AÇO INOX AISI 420</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>03.022-007318</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>01.09.1.1.27.3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007333 - CONJUNTO PLACA CENTRAL USINADO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
         <v>1</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>03.022-007329</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>2</v>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>03.022-007329</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.022-007333</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007330 - PRENSA GAXETA</t>
+          <t xml:space="preserve">        03.022-007331 - PLACA CENTRAL SOLDADA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1980,73 +1980,73 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007333</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>03.022-007330</t>
+          <t>03.022-007331</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007340 - PLACA CENTRAL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3.44</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>03.022-007330</t>
+          <t>03.022-007331</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.3</t>
+          <t>03.022-007340</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">                01.09.3.1.2.4.6 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>11.95</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>03.022-007330</t>
+          <t>03.022-007340</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007334 - CHAVETA CENTRAL</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2059,94 +2059,94 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007340</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>03.022-007334</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.1.10.224.1.22 - BARRA CHAVETA 17 x 25 AÇO CARBONO SAE 1045</t>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007332 - BUCHA DA PLACA CENTRAL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>03.022-007331</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>03.022-007332</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.13.1.58.12.24 - TUBO Ø50 x Ø27 SAE 8550 .</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>155</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>03.022-007334</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>01.09.1.10.224.1.22</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007318 - EIXO PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007332</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>03.022-007318</t>
+          <t>01.13.1.58.12.24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.1.1.27.3.7 - BARRA REDONDA 3" AÇO INOX AISI 420</t>
+          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1250</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>03.022-007318</t>
+          <t>03.022-007332</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>01.09.1.1.27.3.7</t>
+          <t>09.1.0002</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007333 - CONJUNTO PLACA CENTRAL USINADO</t>
+          <t xml:space="preserve">            03.022-007371 - TAMPÃO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2155,48 +2155,48 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007331</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>03.022-007333</t>
+          <t>03.022-007371</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        03.022-007331 - PLACA CENTRAL SOLDADA</t>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.09.1.1.225.1.9 - BARRA REDONDA 6 mm AÇO CARBONO SAE 1020</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>03.022-007333</t>
+          <t>03.022-007371</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>01.09.1.1.225.1.9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007340 - PLACA CENTRAL</t>
+          <t xml:space="preserve">            03.022-007336 - BUCHA CENTRAL 2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2214,39 +2214,39 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>03.022-007340</t>
+          <t>03.022-007336</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.09.3.1.2.4.6 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+          <t xml:space="preserve">                01.13.1.59.12.24 - TUBO Ø110 x Ø90 SAE 8550 .</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>11.95</v>
+        <v>30</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>03.022-007340</t>
+          <t>03.022-007336</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.6</t>
+          <t>01.13.1.59.12.24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2259,19 +2259,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>03.022-007340</t>
+          <t>03.022-007336</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>09.1.0002</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007332 - BUCHA DA PLACA CENTRAL</t>
+          <t xml:space="preserve">    03.022-007335 - BUCHA CENTRAL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2284,19 +2284,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>03.022-007332</t>
+          <t>03.022-007335</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.13.1.58.12.24 - TUBO Ø50 x Ø27 SAE 8550 .</t>
+          <t xml:space="preserve">        01.13.1.60.12.24 - TUBO Ø105 x Ø60 SAE 8550 .</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2305,23 +2305,23 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>03.022-007332</t>
+          <t>03.022-007335</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>01.13.1.58.12.24</t>
+          <t>01.13.1.60.12.24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>03.022-007332</t>
+          <t>03.022-007335</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2346,7 +2346,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007371 - TAMPÃO</t>
+          <t xml:space="preserve">    03.022-007342 - CONJUNTO ALAVANCA USINADA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2359,44 +2359,44 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007342</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                01.09.1.1.225.1.9 - BARRA REDONDA 6 mm AÇO CARBONO SAE 1020</t>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        03.022-007341 - CONJUNTO ALAVANCA SOLDADA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007342</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01.09.1.1.225.1.9</t>
+          <t>03.022-007341</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007336 - BUCHA CENTRAL 2</t>
+          <t xml:space="preserve">            03.022-007344 - TUBO DA ALAVANCA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2405,23 +2405,23 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>03.022-007331</t>
+          <t>03.022-007341</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>03.022-007336</t>
+          <t>03.022-007344</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.13.1.59.12.24 - TUBO Ø110 x Ø90 SAE 8550 .</t>
+          <t xml:space="preserve">                01.13.1.61.1.24 - TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2430,23 +2430,23 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>03.022-007336</t>
+          <t>03.022-007344</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>01.13.1.59.12.24</t>
+          <t>01.13.1.61.1.24</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007343 - CHAPA DA ALAVANCA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2455,73 +2455,73 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>03.022-007336</t>
+          <t>03.022-007341</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>03.022-007343</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007335 - BUCHA CENTRAL</t>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007343</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>03.022-007335</t>
+          <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.13.1.60.12.24 - TUBO Ø105 x Ø60 SAE 8550 .</t>
+          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>03.022-007335</t>
+          <t>03.022-007343</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01.13.1.60.12.24</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007345 - BARRA SUPERIOR DA ALAVANCA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2530,48 +2530,48 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>03.022-007335</t>
+          <t>03.022-007341</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>03.022-007345</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007342 - CONJUNTO ALAVANCA USINADA</t>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007345</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>03.022-007342</t>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        03.022-007341 - CONJUNTO ALAVANCA SOLDADA</t>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2584,19 +2584,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>03.022-007342</t>
+          <t>03.022-007345</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007344 - TUBO DA ALAVANCA</t>
+          <t xml:space="preserve">            03.022-007350 - BARRA INFERIOR DA ALAVANCA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2614,39 +2614,39 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>03.022-007344</t>
+          <t>03.022-007350</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.13.1.61.1.24 - TUBO Ø4" x Ø60 ASTM A106 GR C .</t>
+          <t xml:space="preserve">                01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>180</v>
+        <v>0.54</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>03.022-007344</t>
+          <t>03.022-007350</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>01.13.1.61.1.24</t>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007343 - CHAPA DA ALAVANCA</t>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2659,69 +2659,69 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007350</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>03.022-007343</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007351 - BUCHA DO CONJUNTO ALAVANCA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>03.022-007343</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.3</t>
+          <t>03.022-007351</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.13.1.62.12.24 - TUBO Ø35 x Ø55 SAE 8550 .</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>03.022-007343</t>
+          <t>03.022-007351</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.13.1.62.12.24</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007345 - BARRA SUPERIOR DA ALAVANCA</t>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2734,44 +2734,44 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007351</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>03.022-007345</t>
+          <t>09.1.0002</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007352 - CONJUNTO SUPORTE DO DISCO USINADO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>03.022-007345</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.11</t>
+          <t>03.022-007352</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        03.022-007337 - CONJUNTO SUPORTE DO DISCO SOLDADO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2780,23 +2780,23 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>03.022-007345</t>
+          <t>03.022-007352</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.022-007337</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007350 - BARRA INFERIOR DA ALAVANCA</t>
+          <t xml:space="preserve">            03.022-007338 - BASE DO SUPORTE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2805,16 +2805,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>03.022-007341</t>
+          <t>03.022-007337</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>03.022-007350</t>
+          <t>03.022-007338</t>
         </is>
       </c>
     </row>
@@ -2830,11 +2830,11 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.54</v>
+        <v>2.83</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>03.022-007350</t>
+          <t>03.022-007338</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2855,11 +2855,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>03.022-007350</t>
+          <t>03.022-007338</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2871,7 +2871,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007351 - BUCHA DO CONJUNTO ALAVANCA</t>
+          <t xml:space="preserve">            03.022-007339 - CHAPA DO SUPORTE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2884,44 +2884,44 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007337</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>03.022-007351</t>
+          <t>03.022-007339</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.13.1.62.12.24 - TUBO Ø35 x Ø55 SAE 8550 .</t>
+          <t xml:space="preserve">                01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>40</v>
+        <v>6.52</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>03.022-007351</t>
+          <t>03.022-007339</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>01.13.1.62.12.24</t>
+          <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2934,19 +2934,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>03.022-007351</t>
+          <t>03.022-007339</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007352 - CONJUNTO SUPORTE DO DISCO USINADO</t>
+          <t xml:space="preserve">            03.022-007353 - BUCHA MAIOR DO SUPORTE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2955,123 +2955,123 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007337</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>03.022-007352</t>
+          <t>03.022-007353</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        03.022-007337 - CONJUNTO SUPORTE DO DISCO SOLDADO</t>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.13.1.63.12.24 - TUBO Ø60 x Ø30 SAE 8550 .</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>03.022-007352</t>
+          <t>03.022-007353</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>01.13.1.63.12.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>03.022-007353</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>09.1.0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007354 - BUCHA MENOR DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>03.022-007337</t>
         </is>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007338 - BASE DO SUPORTE</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>03.022-007337</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>03.022-007338</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>03.022-007338</t>
-        </is>
-      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.11</t>
+          <t>03.022-007354</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">                01.13.1.58.12.24 - TUBO Ø50 x Ø27 SAE 8550 .</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>03.022-007338</t>
+          <t>03.022-007354</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.13.1.58.12.24</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007339 - CHAPA DO SUPORTE</t>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3084,69 +3084,69 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>03.022-007354</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>09.1.0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007371 - TAMPÃO</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>UNID</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
           <t>03.022-007337</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>03.022-007339</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>03.022-007339</t>
-        </is>
-      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.3</t>
+          <t>03.022-007371</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">                01.09.1.1.225.1.9 - BARRA REDONDA 6 mm AÇO CARBONO SAE 1020</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>03.022-007339</t>
+          <t>03.022-007371</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.1.1.225.1.9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007353 - BUCHA MAIOR DO SUPORTE</t>
+          <t xml:space="preserve">    03.022-007357 - BUCHA DO BRAÇO ARTICULADO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3155,23 +3155,23 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>03.022-007353</t>
+          <t>03.022-007357</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.13.1.63.12.24 - TUBO Ø60 x Ø30 SAE 8550 .</t>
+          <t xml:space="preserve">        01.13.1.58.12.24 - TUBO Ø50 x Ø27 SAE 8550 .</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3180,23 +3180,23 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>03.022-007353</t>
+          <t>03.022-007357</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>01.13.1.63.12.24</t>
+          <t>01.13.1.58.12.24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3205,11 +3205,11 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>03.022-007353</t>
+          <t>03.022-007357</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007354 - BUCHA MENOR DO SUPORTE</t>
+          <t xml:space="preserve">    03.022-007356 - BRAÇO ARTICULADO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3234,44 +3234,44 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>03.022-007354</t>
+          <t>03.022-007356</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.13.1.58.12.24 - TUBO Ø50 x Ø27 SAE 8550 .</t>
+          <t xml:space="preserve">        01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>50</v>
+        <v>3.72</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>03.022-007354</t>
+          <t>03.022-007356</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>01.13.1.58.12.24</t>
+          <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3284,19 +3284,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>03.022-007354</t>
+          <t>03.022-007356</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            03.022-007371 - TAMPÃO</t>
+          <t xml:space="preserve">    03.022-007319 - MANCAL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3309,19 +3309,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>03.022-007337</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007319</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.09.1.1.225.1.9 - BARRA REDONDA 6 mm AÇO CARBONO SAE 1020</t>
+          <t xml:space="preserve">        01.09.1.1.44.1.9 - BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3330,23 +3330,23 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007319</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>01.09.1.1.225.1.9</t>
+          <t>01.09.1.1.44.1.9</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007357 - BUCHA DO BRAÇO ARTICULADO</t>
+          <t xml:space="preserve">    03.022-007361 - ANEL DE AJUSTE MAIOR</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3364,39 +3364,39 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>03.022-007357</t>
+          <t>03.022-007361</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.13.1.58.12.24 - TUBO Ø50 x Ø27 SAE 8550 .</t>
+          <t xml:space="preserve">        01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>80</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>03.022-007357</t>
+          <t>03.022-007361</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>01.13.1.58.12.24</t>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3405,23 +3405,23 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>03.022-007357</t>
+          <t>03.022-007361</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007356 - BRAÇO ARTICULADO</t>
+          <t xml:space="preserve">    03.022-007364 - ANEL DE AJUSTE DO EIXO</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>03.022-007356</t>
+          <t>03.022-007364</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+          <t xml:space="preserve">        01.09.3.1.2.4.6 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3455,16 +3455,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>03.022-007356</t>
+          <t>03.022-007364</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.3</t>
+          <t>01.09.3.1.2.4.6</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>03.022-007356</t>
+          <t>03.022-007364</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007319 - MANCAL</t>
+          <t xml:space="preserve">    03.022-007360 - ANEL DE AJUSTE MENOR</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3514,39 +3514,39 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>03.022-007319</t>
+          <t>03.022-007360</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.1.1.44.1.9 - BARRA REDONDA 7" AÇO CARBONO SAE 1020</t>
+          <t xml:space="preserve">        01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>140</v>
+        <v>0.8</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>03.022-007319</t>
+          <t>03.022-007360</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>01.09.1.1.44.1.9</t>
+          <t>01.09.3.1.2.4.11</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007361 - ANEL DE AJUSTE MAIOR</t>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3555,73 +3555,73 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007360</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>03.022-007361</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007358 - PINO MAIOR</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>03.022-007361</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.11</t>
+          <t>03.022-007358</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.09.1.1.17.1.27 - BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>03.022-007361</t>
+          <t>03.022-007358</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.1.1.17.1.27</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007364 - ANEL DE AJUSTE DO EIXO</t>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3630,73 +3630,73 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007358</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>03.022-007364</t>
+          <t>09.1.0002</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.3.1.2.4.6 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1"</t>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007363 - PINO MENOR DO BRAÇO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3.78</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>03.022-007364</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.6</t>
+          <t>03.022-007363</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.09.1.1.15.1.27 - BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>03.022-007364</t>
+          <t>03.022-007363</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.1.1.15.1.27</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007360 - ANEL DE AJUSTE MENOR</t>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3705,73 +3705,73 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007363</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>03.022-007360</t>
+          <t>09.1.0002</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.3.1.2.4.11 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 1/2"</t>
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007359 - PINO MENOR</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>03.022-007360</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.11</t>
+          <t>03.022-007359</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">        01.09.1.1.15.1.27 - BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>03.022-007360</t>
+          <t>03.022-007359</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.1.1.15.1.27</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007358 - PINO MAIOR</t>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3784,69 +3784,69 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007359</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>03.022-007358</t>
+          <t>09.1.0002</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.1.1.17.1.27 - BARRA REDONDA 1 3/4" AÇO CARBONO SAE 8550</t>
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007371 - TAMPÃO</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>03.022-007358</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>01.09.1.1.17.1.27</t>
+          <t>03.022-007371</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+          <t xml:space="preserve">        01.09.1.1.225.1.9 - BARRA REDONDA 6 mm AÇO CARBONO SAE 1020</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>03.022-007358</t>
+          <t>03.022-007371</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>01.09.1.1.225.1.9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007363 - PINO MENOR DO BRAÇO</t>
+          <t xml:space="preserve">    03.022-007325 - TAMPA LATERAL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3864,39 +3864,39 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>03.022-007363</t>
+          <t>03.022-007325</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.1.1.15.1.27 - BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+          <t xml:space="preserve">        01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>100</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>03.022-007363</t>
+          <t>03.022-007325</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>01.09.1.1.15.1.27</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007320 - SUPORTE DO ATUADOR USINADO</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3909,19 +3909,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>03.022-007363</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>03.022-007320</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007359 - PINO MENOR</t>
+          <t xml:space="preserve">        03.022-007321 - SUPORTE DO ATUADOR SOLDADO</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3934,69 +3934,69 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007320</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>03.022-007359</t>
+          <t>03.022-007321</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        01.09.1.1.15.1.27 - BARRA REDONDA 1 1/2" AÇO CARBONO SAE 8550</t>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            03.022-007324 - CHAPA DE CONTATO DA VÁLVULA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>03.022-007359</t>
+          <t>03.022-007321</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>01.09.1.1.15.1.27</t>
+          <t>03.022-007324</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">        09.1.0002 - SERVIÇO DE TRATAMENTO TÉRMICO</t>
+          <t xml:space="preserve">                01.09.3.1.1.5.4 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>9.35</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>03.022-007359</t>
+          <t>03.022-007324</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>09.1.0002</t>
+          <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007371 - TAMPÃO</t>
+          <t xml:space="preserve">            03.022-007322 - BASE DE LIGAÇÃO</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4005,48 +4005,48 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007321</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007322</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.1.1.225.1.9 - BARRA REDONDA 6 mm AÇO CARBONO SAE 1020</t>
+          <t xml:space="preserve">                01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>80</v>
+        <v>4.76</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>03.022-007371</t>
+          <t>03.022-007322</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>01.09.1.1.225.1.9</t>
+          <t>01.09.3.1.1.5.3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007325 - TAMPA LATERAL</t>
+          <t xml:space="preserve">            03.022-007323 - CHAPA DE CONTROLE DO ATUADOR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4055,23 +4055,23 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007321</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>03.022-007325</t>
+          <t>03.022-007323</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">        01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+          <t xml:space="preserve">                01.09.3.1.1.5.4 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4080,23 +4080,23 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>8.539999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>03.022-007325</t>
+          <t>03.022-007323</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.3</t>
+          <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03.022-007347-REC - CONJUNTO DISCO USINADO</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4105,23 +4105,23 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>03.022-007325</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.022-007347-REC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    03.022-007320 - SUPORTE DO ATUADOR USINADO</t>
+          <t xml:space="preserve">        03.022-007346-1 - CONJUNTO DISCO SOLDADO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4134,19 +4134,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>04.01.3.000598</t>
+          <t>03.022-007347-REC</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>03.022-007320</t>
+          <t>03.022-007346-1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        03.022-007321 - SUPORTE DO ATUADOR SOLDADO</t>
+          <t xml:space="preserve">            03.022-007349 - BASE DO DISCO</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4159,69 +4159,69 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>03.022-007320</t>
+          <t>03.022-007346-1</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>03.022-007349</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007324 - CHAPA DE CONTATO DA VÁLVULA</t>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>4.27</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>03.022-007349</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>03.022-007324</t>
+          <t>01.09.3.1.2.4.3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.09.3.1.1.5.4 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>9.35</v>
+        <v>1</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>03.022-007324</t>
+          <t>03.022-007349</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.4</t>
+          <t>09.1.0003</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">    01.05.1.103 - ROLAMENTO AUTOCOMPENSADOR DE ROLOS SKF 22312 E</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4230,23 +4230,23 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>03.022-007324</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.05.1.103</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007322 - BASE DE LIGAÇÃO</t>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    01.03.7.2.2.1.14 - ANEL ELÁSTICO EXTERNO DIN 471 AÇO MOLA 60 mm</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4259,19 +4259,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>03.022-007322</t>
+          <t>01.03.7.2.2.1.14</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.09.3.1.1.5.3 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 5/8"</t>
+          <t xml:space="preserve">    01.04.1.11.7.10 - GAXETA QUADRADA TRANÇADA 3/8" FIOS DE CARBONO E GRAFITE FLEXÍVEL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4280,23 +4280,23 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4.76</v>
+        <v>0.5</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>03.022-007322</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.3</t>
+          <t>01.04.1.11.7.10</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">    01.03.5.8.7.8.9.12 - PINO ROSCADO DIN 976 AÇO CARBONO ZINCADO PRETO Ø12 X 60 mm</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4305,23 +4305,23 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>03.022-007322</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.03.5.8.7.8.9.12</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007323 - CHAPA DE CONTROLE DO ATUADOR</t>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    01.03.3.1.2.69 - ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-13</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4330,48 +4330,48 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>03.022-007321</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>03.022-007323</t>
+          <t>01.03.3.1.2.69</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.09.3.1.1.5.4 - CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
+          <t xml:space="preserve">    01.03.2.1.4.2.7 - PORCA SEXTAVADA - DIN 934 CL. 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>9.35</v>
+        <v>4</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>03.022-007323</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>01.09.3.1.1.5.4</t>
+          <t>01.03.2.1.4.2.7</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.15.19 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M30 - P.3,5 x 100</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4384,19 +4384,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>03.022-007323</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.03.1.1.1.1.2.15.19</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    03.022-007347-REC - CONJUNTO DISCO USINADO</t>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    01.03.3.3.2.72 - ARRUELA PRESSÃO - DIN 127-A AÇO CARBONO ZINCADO PRETO A-31</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>03.022-007347-REC</t>
+          <t>01.03.3.3.2.72</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        03.022-007346-1 - CONJUNTO DISCO SOLDADO</t>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    01.03.2.1.1.1.15 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO BRANCO M30 - P.3,5</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4434,19 +4434,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>03.022-007347-REC</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>03.022-007346-1</t>
+          <t>01.03.2.1.1.1.15</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            03.022-007349 - BASE DO DISCO</t>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.9.9 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 50</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4459,44 +4459,44 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>03.022-007346-1</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>03.022-007349</t>
+          <t>01.03.1.1.1.1.2.9.9</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">                01.09.3.1.2.4.3 - CHAPA LISA AÇO CARBONO - ASTM A 516 Gr 70 5/8"</t>
+          <t xml:space="preserve">    01.03.2.1.9.2.9 - PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4.27</v>
+        <v>17</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>03.022-007349</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>01.09.3.1.2.4.3</t>
+          <t>01.03.2.1.9.2.9</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">                09.1.0003 - SERVIÇO DE CORTE DE CHAPA</t>
+          <t xml:space="preserve">    01.04.3.2.1.12.316 - O'RING VITON ISO 3601 70/75 SHORE A Ø641 x 10 mm</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4509,19 +4509,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>03.022-007349</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.04.3.2.1.12.316</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.05.1.103 - ROLAMENTO AUTOCOMPENSADOR DE ROLOS SKF 22312 E</t>
+          <t xml:space="preserve">    01.03.1.7.4.1.2.4.4 - PARAFUSO ALLEN SEM CABEÇA DIN 913 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>01.05.1.103</t>
+          <t>01.03.1.7.4.1.2.4.4</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.7.2.2.1.14 - ANEL ELÁSTICO EXTERNO DIN 471 AÇO MOLA 60 mm</t>
+          <t xml:space="preserve">    01.03.2.1.1.2.4 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4564,23 +4564,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>01.03.7.2.2.1.14</t>
+          <t>01.03.2.1.1.2.4</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.04.1.11.7.10 - GAXETA QUADRADA TRANÇADA 3/8" FIOS DE CARBONO E GRAFITE FLEXÍVEL</t>
+          <t xml:space="preserve">    01.03.2.1.1.2.6 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>01.04.1.11.7.10</t>
+          <t>01.03.2.1.1.2.6</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.5.8.7.8.9.12 - PINO ROSCADO DIN 976 AÇO CARBONO ZINCADO PRETO Ø12 X 60 mm</t>
+          <t xml:space="preserve">    01.03.1.7.4.6.2.6.7 - PARAFUSO ALLEN SEM CABEÇA DIN 913 . AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 40</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4614,14 +4614,14 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>01.03.5.8.7.8.9.12</t>
+          <t>01.03.1.7.4.6.2.6.7</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.3.1.2.69 - ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-13</t>
+          <t xml:space="preserve">    01.03.3.1.2.55 - ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-10.5</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4639,14 +4639,14 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>01.03.3.1.2.69</t>
+          <t>01.03.3.1.2.55</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.2.1.4.2.7 - PORCA SEXTAVADA - DIN 934 CL. 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75</t>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.6.8 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 45</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4664,14 +4664,14 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>01.03.2.1.4.2.7</t>
+          <t>01.03.1.1.1.1.2.6.8</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.15.19 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M30 - P.3,5 x 100</t>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.7.5 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75 x 30</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4689,14 +4689,14 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.15.19</t>
+          <t>01.03.1.1.1.1.2.7.5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.3.3.2.72 - ARRUELA PRESSÃO - DIN 127-A AÇO CARBONO ZINCADO PRETO A-31</t>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.5.5 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M8 - P.1,25 x 30</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4714,14 +4714,14 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>01.03.3.3.2.72</t>
+          <t>01.03.1.1.1.1.2.5.5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.2.1.1.1.15 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO BRANCO M30 - P.3,5</t>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.6.4 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4739,14 +4739,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>01.03.2.1.1.1.15</t>
+          <t>01.03.1.1.1.1.2.6.4</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.9.9 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 50</t>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.9.8 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 45</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.9.9</t>
+          <t>01.03.1.1.1.1.2.9.8</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.2.1.9.2.9 - PORCA SEXTAVADA - DIN 934 Gr. 8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0</t>
+          <t xml:space="preserve">    01.03.1.1.1.1.2.9.12 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 65</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4789,14 +4789,14 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>01.03.2.1.9.2.9</t>
+          <t>01.03.1.1.1.1.2.9.12</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.04.3.2.1.12.316 - O'RING VITON ISO 3601 70/75 SHORE A Ø641 x 10 mm</t>
+          <t xml:space="preserve">    01.13.3.349 - NIPLE INOX 304 – 1/4" NPT</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4814,14 +4814,14 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>01.04.3.2.1.12.316</t>
+          <t>01.13.3.349</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.7.4.1.2.4.4 - PARAFUSO ALLEN SEM CABEÇA DIN 913 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 25</t>
+          <t xml:space="preserve">    01.13.3.14 - TAMPÃO ASTM A 197 1" NPT - ANSI B16.3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -4839,14 +4839,14 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>01.03.1.7.4.1.2.4.4</t>
+          <t>01.13.3.14</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.2.1.1.2.4 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0</t>
+          <t xml:space="preserve">    01.13.3.10 - UNIÃO ORIENTÁVEL SIMPLES TUBO AISI 304 - 10 mm X 1/4" - NPT</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>01.03.2.1.1.2.4</t>
+          <t>01.13.3.10</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.2.1.1.2.6 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
+          <t xml:space="preserve">    01.13.3.125 - DISTRIBUIDOR DE GRAXA BM4 – 4 MÓDULOS / 8 SAÍDAS EXIMPORT</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4889,14 +4889,14 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>01.03.2.1.1.2.6</t>
+          <t>01.13.3.125</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.7.4.6.2.6.7 - PARAFUSO ALLEN SEM CABEÇA DIN 913 . AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 40</t>
+          <t xml:space="preserve">    01.03.3.1.2.71 - ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-8,1</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>01.03.1.7.4.6.2.6.7</t>
+          <t>01.03.3.1.2.71</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.3.1.2.55 - ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-10.5</t>
+          <t xml:space="preserve">    01.03.2.1.1.2.6 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4939,14 +4939,14 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>01.03.3.1.2.55</t>
+          <t>01.03.2.1.1.2.6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.6.8 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 45</t>
+          <t xml:space="preserve">    01.13.2.6.1 - TÊ FÊMEA 1/4" NPT AISI 304</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.6.8</t>
+          <t>01.13.2.6.1</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.7.5 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75 x 30</t>
+          <t xml:space="preserve">    01.13.1.13.2.10 - TUBO 10 mm AISI 304 PD 1,0 mm</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6</v>
+        <v>6000</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4989,14 +4989,14 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.7.5</t>
+          <t>01.13.1.13.2.10</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.5.5 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M8 - P.1,25 x 30</t>
+          <t xml:space="preserve">    01.13.3.17 - CONEXÃO JOELHO TUBO 10 mm X 1/4" NPT INOX AISI 304</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.5.5</t>
+          <t>01.13.3.17</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.6.4 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5 x 25</t>
+          <t xml:space="preserve">    01.03.1.14.3.1.2.4.10 - PARAFUSO ALLEN CABEÇA CILÍNDRICA SEXTAVADO INTERNO DIN 912 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 55</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5039,23 +5039,23 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.6.4</t>
+          <t>01.03.1.14.3.1.2.4.10</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.9.8 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 45</t>
+          <t xml:space="preserve">    01.04.1.11.3.10 - GAXETA QUADRADA TRANÇADA 1/4" FIOS DE CARBONO E GRAFITE FLEXÍVEL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5064,14 +5064,14 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.9.8</t>
+          <t>01.04.1.11.3.10</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">    01.03.1.1.1.1.2.9.12 - PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M16 - P.2,0 x 65</t>
+          <t xml:space="preserve">    01.13.3.493 - JUNTA METALBEST TIPO 927 INOX / GRAFITE Ø200 x Ø175 x 3,0 mm</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5089,339 +5089,39 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>01.03.1.1.1.1.2.9.12</t>
+          <t>01.13.3.493</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.3.349 - NIPLE INOX 304 – 1/4" NPT</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>10</v>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>01.13.3.349</t>
-        </is>
-      </c>
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [DEFINIR] PENDENTE: balões 52, 62, 65 sem linha na lista do desenho</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr"/>
+      <c r="C187" s="3" t="inlineStr"/>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.3.14 - TAMPÃO ASTM A 197 1" NPT - ANSI B16.3</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>2</v>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>01.13.3.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.3.10 - UNIÃO ORIENTÁVEL SIMPLES TUBO AISI 304 - 10 mm X 1/4" - NPT</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>2</v>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>01.13.3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.3.125 - DISTRIBUIDOR DE GRAXA BM4 – 4 MÓDULOS / 8 SAÍDAS EXIMPORT</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>1</v>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>01.13.3.125</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.03.3.1.2.71 - ARRUELA LISA - DIN 125 A AÇO CARBONO ZINCADO PRETO A-8,1</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>2</v>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>01.03.3.1.2.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.03.2.1.1.2.6 - PORCA SEXTAVADA - DIN 934 CL. 8 AÇO CARBONO ZINCADO PRETO M10 - P.1,5</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>2</v>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>01.03.2.1.1.2.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.2.6.1 - TÊ FÊMEA 1/4" NPT AISI 304</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>4</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>01.13.2.6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.1.13.2.10 - TUBO 10 mm AISI 304 PD 1,0 mm</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>01.13.1.13.2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.3.17 - CONEXÃO JOELHO TUBO 10 mm X 1/4" NPT INOX AISI 304</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>2</v>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>01.13.3.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.03.1.14.3.1.2.4.10 - PARAFUSO ALLEN CABEÇA CILÍNDRICA SEXTAVADO INTERNO DIN 912 CL 8.8 AÇO CARBONO ZINCADO PRETO M6 - P.1,0 x 55</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>2</v>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>01.03.1.14.3.1.2.4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.04.1.11.3.10 - GAXETA QUADRADA TRANÇADA 1/4" FIOS DE CARBONO E GRAFITE FLEXÍVEL</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>01.04.1.11.3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    01.13.3.493 - JUNTA METALBEST TIPO 927 INOX / GRAFITE Ø200 x Ø175 x 3,0 mm</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>2</v>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>01.13.3.493</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [DEFINIR] PENDENTE: balões 52, 62, 65 sem linha na lista do desenho</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr"/>
-      <c r="C199" s="3" t="inlineStr"/>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="3" t="inlineStr">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    [DEFINIR] PENDENTE: desenho 022-007345 (barra superior da alavanca) sem desenho</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr"/>
-      <c r="C200" s="3" t="inlineStr"/>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr"/>
+      <c r="B188" s="3" t="inlineStr"/>
+      <c r="C188" s="3" t="inlineStr"/>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>04.01.3.000598</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5434,7 +5134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6118,25 +5818,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03.022-007313</t>
+          <t>03.022-007324</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.3.1.1.5.4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>9.35</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
     </row>
@@ -6148,21 +5848,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>03.022-007314</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.03.1.1.1.1.2.7.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
+          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75 x 30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6173,56 +5873,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Só na minha lista (falta no Nomus)</t>
+          <t>Só no Nomus (não está na minha lista)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>03.022-007315</t>
+          <t>03.022-007324</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>01.09.3.1.1.5.52</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
+          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>Kg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Só na minha lista (falta no Nomus)</t>
+          <t>Só no Nomus (não está na minha lista)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03.022-007316</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.04.01.3.000598-19-REC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>4</v>
+          <t>BUCHA ESTRIADA</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6233,26 +5933,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Só na minha lista (falta no Nomus)</t>
+          <t>Só no Nomus (não está na minha lista)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03.022-007317</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.04.01.3.000598-21-REC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>4</v>
+          <t>TAMPA JANELA DE INSPEÇÃO</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6263,26 +5963,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Só na minha lista (falta no Nomus)</t>
+          <t>Só no Nomus (não está na minha lista)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03.022-007322</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.04.01.3.000598-22-REC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
+          <t>ATUADOR</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -6293,388 +5993,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Só na minha lista (falta no Nomus)</t>
+          <t>Só no Nomus (não está na minha lista)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03.022-007323</t>
+          <t>04.01.3.000598</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>09.1.0003</t>
+          <t>03.04.01.3.000598-23-REC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
+          <t>CHAVETA MENOR</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Só na minha lista (falta no Nomus)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>03.022-007324</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.4</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 3/4"</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Só na minha lista (falta no Nomus)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>03.022-007324</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>09.1.0003</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Só na minha lista (falta no Nomus)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>03.022-007325</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>09.1.0003</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Só na minha lista (falta no Nomus)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>03.022-007329</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>09.1.0003</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Só na minha lista (falta no Nomus)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>03.022-007330</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>09.1.0003</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Só na minha lista (falta no Nomus)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>03.022-007366</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>09.1.0003</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SERVIÇO DE CORTE DE CHAPA</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Só na minha lista (falta no Nomus)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>01.03.1.1.1.1.2.7.5</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PARAFUSO SEXTAVADO DIN933 CL 8.8 AÇO CARBONO ZINCADO PRETO M12 - P.1,75 x 30</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>6</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Só no Nomus (não está na minha lista)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>03.022-007324</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>01.09.3.1.1.5.52</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CHAPA LISA AÇO CARBONO - ASTM A 36 - 1"</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>10</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Só no Nomus (não está na minha lista)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>03.04.01.3.000598-19-REC</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>BUCHA ESTRIADA</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Só no Nomus (não está na minha lista)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>03.04.01.3.000598-21-REC</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TAMPA JANELA DE INSPEÇÃO</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Só no Nomus (não está na minha lista)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>03.04.01.3.000598-22-REC</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ATUADOR</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>UNID</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Só no Nomus (não está na minha lista)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>04.01.3.000598</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>03.04.01.3.000598-23-REC</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>CHAVETA MENOR</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>UNID</t>
         </is>

--- a/Lista_de_materiais_04.01.3.000598_estilo_Nomus.xlsx
+++ b/Lista_de_materiais_04.01.3.000598_estilo_Nomus.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,8 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +474,16 @@
           <t>Código do componente</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Serviço aplicado em (peça)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Observação do serviço</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -692,6 +704,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>03.022-007308 - FLANGE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -917,6 +939,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>03.022-007310 - CHAPA INFERIOR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -992,6 +1024,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>03.022-007311 - CHAPA LATERAL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1342,6 +1384,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>03.022-007355 - SUPORTE DO DISTRIBUIDOR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1417,6 +1469,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>03.022-007326 - ANEL GUARDA PÓ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1642,6 +1704,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>03.022-007365 - FLANGE DA TAMPA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2067,6 +2139,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>03.022-007340 - PLACA CENTRAL</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2142,6 +2224,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>03.022-007332 - BUCHA DA PLACA CENTRAL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2267,6 +2359,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>03.022-007336 - BUCHA CENTRAL 2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2342,6 +2444,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>03.022-007335 - BUCHA CENTRAL</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Nitretação à gás (desenho 022-007335, nota 3)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2517,6 +2629,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>03.022-007343 - CHAPA DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2592,6 +2714,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>03.022-007345 - BARRA SUPERIOR DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2667,6 +2799,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>03.022-007350 - BARRA INFERIOR DA ALAVANCA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2742,6 +2884,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>03.022-007351 - BUCHA DO CONJUNTO ALAVANCA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2867,6 +3019,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>03.022-007338 - BASE DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2942,6 +3104,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>03.022-007339 - CHAPA DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3017,6 +3189,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>03.022-007353 - BUCHA MAIOR DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3092,6 +3274,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>03.022-007354 - BUCHA MENOR DO SUPORTE</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3217,6 +3409,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>03.022-007357 - BUCHA DO BRAÇO ARTICULADO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3292,6 +3494,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>03.022-007356 - BRAÇO ARTICULADO</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3417,6 +3629,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>03.022-007361 - ANEL DE AJUSTE MAIOR</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3492,6 +3714,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>03.022-007364 - ANEL DE AJUSTE DO EIXO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3567,6 +3799,16 @@
           <t>09.1.0003</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>03.022-007360 - ANEL DE AJUSTE MENOR</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3642,6 +3884,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>03.022-007358 - PINO MAIOR</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3717,6 +3969,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>03.022-007363 - PINO MENOR DO BRAÇO</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3792,6 +4054,16 @@
           <t>09.1.0002</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>03.022-007359 - PINO MENOR</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Nitretação em sais (nota do desenho da peça)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -4215,6 +4487,16 @@
       <c r="E151" t="inlineStr">
         <is>
           <t>09.1.0003</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>03.022-007349 - BASE DO DISCO</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Chapa A516 / espessura fora da faixa de corte interno</t>
         </is>
       </c>
     </row>
